--- a/reports/pdf_rolling5_20260813.xlsx
+++ b/reports/pdf_rolling5_20260813.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-06 ~ 2026-08-13  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-06 ~ 2026-08-13  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,732억   ·   현금 267억(5.5%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 7종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,732억   ·   현금 263억(5.4%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 11종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>123</v>
+        <v>244</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1472767560</v>
+        <v>2871128480</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.32%</t>
+          <t>0.00%→0.63%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>0→123</t>
+          <t>0→244</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-189</v>
+        <v>-285</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1879998120</v>
+        <v>-2943953100</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.74%→1.19%</t>
+          <t>1.74%→1.02%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>737→548</t>
+          <t>737→452</t>
         </is>
       </c>
     </row>
@@ -709,11 +709,11 @@
         <v>84</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>989289840</v>
+        <v>977998560</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>1.66%→1.92%</t>
+          <t>1.66%→1.90%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -730,11 +730,11 @@
         <v>-57</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1933166400</v>
+        <v>-1874228400</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>1.05%→0.61%</t>
+          <t>1.05%→0.59%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
@@ -746,23 +746,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1505400600</v>
+        <v>931530600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.39%</t>
+          <t>0.28%→0.49%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>75→98</t>
+          <t>47→80</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -771,595 +771,659 @@
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-23</v>
+        <v>-35</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1474484000</v>
+        <v>-2352350000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>1.14%→0.67%</t>
+          <t>1.14%→0.53%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>71→48</t>
+          <t>71→36</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>877142200</v>
+        <v>436896020</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>1.19%→1.30%</t>
+          <t>1.06%→1.07%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>99→116</t>
+          <t>318→349</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-13</v>
+        <v>-33</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-339410500</v>
+        <v>-3569161200</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.20%</t>
+          <t>5.39%→4.34%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>49→36</t>
+          <t>217→184</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>한국피아이엠  (신규)</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1495577600</v>
+        <v>1958085800</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>2.73%→3.37%</t>
+          <t>0.00%→0.43%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>150→166</t>
+          <t>0→29</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-225153500</v>
+        <v>-341426800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.09%→0.05%</t>
+          <t>0.33%→0.21%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>49→36</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1414512000</v>
+        <v>1507778800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.60%→0.90%</t>
+          <t>1.01%→1.40%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>23→35</t>
+          <t>75→98</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2015059200</v>
+        <v>-211173820</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.86%→0.47%</t>
+          <t>0.09%→0.05%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>25→13</t>
+          <t>26→13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1693175000</v>
+        <v>847259600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>5.01%→5.89%</t>
+          <t>1.19%→1.26%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>75→80</t>
+          <t>99→116</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1413271200</v>
+        <v>-2158992000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>5.39%→5.25%</t>
+          <t>0.86%→0.51%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>217→205</t>
+          <t>25→13</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>1439328000</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>2.73%→3.25%</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>150→166</t>
+        </is>
+      </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>-984368000</v>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>1.03%→0.86%</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>50→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>1392177600</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>0.60%→0.88%</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>23→35</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
           <t>원익IPS  (편출)</t>
         </is>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H14" s="15" t="n">
         <v>-9</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I14" s="15" t="n">
         <v>-909196200</v>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>0.21%→0.00%</t>
         </is>
       </c>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>9→0</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="G14" s="14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>1641475000</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>5.01%→5.72%</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>75→80</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>한중엔시에스</t>
         </is>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H15" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I14" s="15" t="n">
-        <v>-300273600</v>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>0.65%→0.60%</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="I15" s="15" t="n">
+        <v>-301928000</v>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>0.65%→0.61%</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>82→74</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>775500000</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>2.22%→2.76%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>46→49</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>로보티즈</t>
         </is>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H16" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I15" s="15" t="n">
-        <v>-755337000</v>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>3.38%→3.01%</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="I16" s="15" t="n">
+        <v>-767745000</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>3.38%→3.07%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>58→55</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,183억   ·   현금 21억(0.5%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>큐라클</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>656294760</v>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>1.34%→1.62%</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>986→1,092</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>-33</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>-2048438700</v>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>5.60%→4.91%</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>363→330</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>큐라클</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1281834000</v>
+        <v>657420480</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.00%→2.65%</t>
+          <t>1.34%→1.68%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>542→613</t>
+          <t>986→1,092</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-23</v>
+        <v>-33</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-3999757500</v>
+        <v>-2016897300</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>9.72%→9.42%</t>
+          <t>5.60%→5.01%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>249→226</t>
+          <t>363→330</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1251142200</v>
+        <v>1164960900</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>3.09%→3.40%</t>
+          <t>2.00%→2.50%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>652→715</t>
+          <t>542→613</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-11</v>
+        <v>-23</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1229530500</v>
+        <v>-3877627500</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>7.97%→7.66%</t>
+          <t>9.72%→9.46%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>297→286</t>
+          <t>249→226</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>411365700</v>
+        <v>1297976400</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>1.64%→1.82%</t>
+          <t>3.09%→3.66%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>1,066→1,127</t>
+          <t>652→715</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1535121000</v>
+        <v>-1179882000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>5.95%→5.47%</t>
+          <t>7.97%→7.62%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>111→104</t>
+          <t>297→286</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1987108200</v>
+        <v>421083000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>8.53%→9.04%</t>
+          <t>1.64%→1.93%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>755→797</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="17" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="17" t="n"/>
+          <t>1,066→1,127</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-1471932000</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>5.95%→5.43%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>111→104</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>2031128100</v>
+        <v>1935813600</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>8.75%→9.07%</t>
+          <t>8.53%→9.12%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>511→540</t>
+          <t>755→797</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1371,23 +1435,23 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1218379500</v>
+        <v>1747786500</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>2.22%→2.70%</t>
+          <t>8.75%→8.08%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>107→120</t>
+          <t>511→540</t>
         </is>
       </c>
       <c r="G26" s="17" t="n"/>
@@ -1396,950 +1460,1662 @@
       <c r="J26" s="17" t="n"/>
       <c r="K26" s="17" t="n"/>
     </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="n"/>
-      <c r="C28" s="19" t="n"/>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="19" t="n"/>
-      <c r="F28" s="19" t="n"/>
-      <c r="G28" s="19" t="n"/>
-      <c r="H28" s="19" t="n"/>
-      <c r="I28" s="19" t="n"/>
-      <c r="J28" s="19" t="n"/>
-      <c r="K28" s="19" t="n"/>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
-      <c r="J30" s="19" t="n"/>
-      <c r="K30" s="19" t="n"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 291억   ·   현금 15억(5.0%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 9종목  /  매도 12종목</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>1207334700</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>2.22%→2.77%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>107→120</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,694억   ·   현금 60억(2.2%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 4종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>4275180000</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>1.49%→3.20%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>69→139</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-281</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-1970647380</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>1.40%→0.58%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>499→218</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>3938220000</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>1.56%→2.97%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>50→100</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-148</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-3387009600</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>2.53%→1.29%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>298→150</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>533744640</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>0.19%→0.41%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>50→98</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-2556473400</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>1.94%→0.94%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>241→119</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B35" s="11" t="n">
-        <v>224</v>
+        <v>33</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>429856000</v>
+        <v>7355205000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>5.37%→6.89%</t>
+          <t>3.97%→6.97%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>796→1,020</t>
+          <t>50→83</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-296</v>
+        <v>-34</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-195940160</v>
+        <v>-1630184400</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>7.98%→7.30%</t>
+          <t>2.91%→2.08%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>3,430→3,134</t>
+          <t>149→115</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>심텍홀딩스</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>19460560</v>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>0.60%→0.67%</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>547→609</t>
-        </is>
-      </c>
+      <c r="A36" s="17" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>에이프로</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-199</v>
+        <v>-23</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-51043500</v>
+        <v>-2144188800</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.21%</t>
+          <t>2.19%→1.30%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>427→228</t>
+          <t>60→37</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>136807600</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>7.16%→7.66%</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>700→747</t>
-        </is>
-      </c>
+      <c r="A37" s="17" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-117</v>
+        <v>-20</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-225412200</v>
+        <v>-982800000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>3.48%→2.69%</t>
+          <t>1.89%→1.48%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>514→397</t>
+          <t>100→80</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>코스맥스엔비티  (신규)</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>28509120</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.10%</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>0→36</t>
-        </is>
-      </c>
+      <c r="A38" s="17" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-65</v>
+        <v>-5</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-89364600</v>
+        <v>-1432080000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>1.69%→1.37%</t>
+          <t>1.95%→1.40%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>349→284</t>
+          <t>18→13</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>46460320</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>3.10%→3.27%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>646→680</t>
-        </is>
-      </c>
+      <c r="A39" s="17" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>금양그린파워</t>
+          <t>미래에셋벤처투자</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-53</v>
+        <v>-3</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-31901760</v>
+        <v>-34138260</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.68%</t>
+          <t>0.54%→0.54%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>375→322</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>노바렉스  (신규)</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>28006000</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.10%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>0→22</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>오로스테크놀로지</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-38</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>-42540240</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>0.25%→0.10%</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>63→25</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>49749600</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>2.80%→2.98%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>96→102</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>상아프론테크</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>-29</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-32354720</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>0.42%→0.31%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>107→78</t>
-        </is>
-      </c>
+          <t>129→126</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,418억   ·   현금 49억(2.1%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 6종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>58869600</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>2.83%→3.04%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>82→88</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>원익머트리얼즈</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-49795200</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>2.62%→2.44%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>269→251</t>
-        </is>
-      </c>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="8" t="n"/>
+      <c r="J42" s="8" t="n"/>
+      <c r="K42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>31737600</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>2.57%→2.68%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>138→144</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>솔브레인홀딩스</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-40261000</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>0.75%→0.61%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>69→56</t>
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="n"/>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="17" t="n"/>
-      <c r="E44" s="17" t="n"/>
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온제약</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>3500615300</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>2.60%→4.12%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>400→633</t>
+        </is>
+      </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>일동제약  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-13</v>
+        <v>-400</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-28108600</v>
+        <v>-2026648000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.93%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>400→0</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="n"/>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="17" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>2359375200</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>2.34%→3.46%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>201→285</t>
+        </is>
+      </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>네이처셀</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-5</v>
+        <v>-156</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-76190000</v>
+        <v>-1215380400</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>2.36%→2.09%</t>
+          <t>0.69%→0.16%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>44→39</t>
+          <t>202→46</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="n"/>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="17" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>5598632000</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>10.94%→13.38%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>371→453</t>
+        </is>
+      </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-3</v>
+        <v>-120</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-8755200</v>
+        <v>-12877800000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>1.27%→1.24%</t>
+          <t>15.29%→10.96%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>124→121</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 615억   ·   현금 20억(3.2%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 6종목  /  매도 3종목</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n"/>
+          <t>356→236</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>1158258400</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>0.91%→1.46%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>99→151</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>HK이노엔  (편출)</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-1396278000</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>0.64%→0.00%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>1687972000</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>6.20%→6.19%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>329→373</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>펩트론  (편출)</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-1159340000</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>0.53%→0.00%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>20→0</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>2364648000</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>1.37%→2.56%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>60→100</t>
+        </is>
+      </c>
+      <c r="G49" s="17" t="n"/>
+      <c r="H49" s="17" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
+    </row>
+    <row r="51" ht="19" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 291억   ·   현금 15억(5.0%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 9종목  /  매도 12종목</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="8" t="n"/>
+      <c r="J52" s="8" t="n"/>
+      <c r="K52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
+      <c r="I53" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K53" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>알지노믹스</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
-        <v>130</v>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>540676500</v>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>2.62%→3.45%</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>368→498</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>휴젤</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I51" s="15" t="n">
-        <v>-840437500</v>
-      </c>
-      <c r="J51" s="16" t="inlineStr">
-        <is>
-          <t>5.32%→3.76%</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>92→67</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="n">
-        <v>107</v>
-      </c>
-      <c r="C52" s="11" t="n">
-        <v>904043000</v>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>0.94%→2.52%</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>72→179</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n">
-        <v>-21</v>
-      </c>
-      <c r="I52" s="15" t="n">
-        <v>-818422500</v>
-      </c>
-      <c r="J52" s="16" t="inlineStr">
-        <is>
-          <t>9.86%→9.04%</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>160→139</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>앱클론</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="n">
-        <v>89</v>
-      </c>
-      <c r="C53" s="11" t="n">
-        <v>360094000</v>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>3.06%→4.14%</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>525→614</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>파마리서치</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n">
-        <v>-12</v>
-      </c>
-      <c r="I53" s="15" t="n">
-        <v>-595476000</v>
-      </c>
-      <c r="J53" s="16" t="inlineStr">
-        <is>
-          <t>5.13%→4.06%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>61→49</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
-        <v>30</v>
+        <v>224</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>133518000</v>
+        <v>429856000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>3.55%→3.75%</t>
+          <t>5.37%→6.89%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>475→505</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="n"/>
-      <c r="H54" s="17" t="n"/>
-      <c r="I54" s="17" t="n"/>
-      <c r="J54" s="17" t="n"/>
-      <c r="K54" s="17" t="n"/>
+          <t>796→1,020</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-296</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-195940160</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>7.98%→7.30%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>3,430→3,134</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>심텍홀딩스</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>567094500</v>
+        <v>19460560</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.03%→3.12%</t>
+          <t>0.60%→0.67%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>62→89</t>
-        </is>
-      </c>
-      <c r="G55" s="17" t="n"/>
-      <c r="H55" s="17" t="n"/>
-      <c r="I55" s="17" t="n"/>
-      <c r="J55" s="17" t="n"/>
-      <c r="K55" s="17" t="n"/>
+          <t>547→609</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>에이프로</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-199</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-51043500</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.38%→0.21%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>427→228</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>136807600</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>7.16%→7.66%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>700→747</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-117</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-225412200</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>3.48%→2.69%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>514→397</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티  (신규)</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>28509120</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.10%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>0→36</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-65</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-89364600</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>1.69%→1.37%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>349→284</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>46460320</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>3.10%→3.27%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>646→680</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>금양그린파워</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-31901760</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>0.79%→0.68%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>375→322</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>28006000</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.10%</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>0→22</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-38</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-42540240</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>0.25%→0.10%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>63→25</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>49749600</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>2.80%→2.98%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>96→102</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>상아프론테크</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-32354720</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.31%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>107→78</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>31737600</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>2.57%→2.68%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>138→144</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-49795200</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>2.62%→2.44%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>269→251</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>58869600</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>2.83%→3.04%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>82→88</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-40261000</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>0.75%→0.61%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>69→56</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>네패스아크</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-28108600</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.10%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>26→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-76190000</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>2.36%→2.09%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>44→39</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="n"/>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-8755200</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>1.27%→1.24%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>124→121</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 615억   ·   현금 20억(3.3%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 6종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>520565500</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>2.62%→3.46%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>368→498</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-798787500</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>5.32%→3.71%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>92→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>107</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>839104700</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>0.94%→2.43%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>72→179</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-793432500</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>9.86%→9.11%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>160→139</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>327261900</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>3.06%→3.92%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>525→614</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-582624000</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>5.13%→4.13%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>61→49</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>오스코텍</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>138516000</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>3.55%→4.04%</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>475→505</t>
+        </is>
+      </c>
+      <c r="G73" s="17" t="n"/>
+      <c r="H73" s="17" t="n"/>
+      <c r="I73" s="17" t="n"/>
+      <c r="J73" s="17" t="n"/>
+      <c r="K73" s="17" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>561953700</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>2.03%→3.21%</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>62→89</t>
+        </is>
+      </c>
+      <c r="G74" s="17" t="n"/>
+      <c r="H74" s="17" t="n"/>
+      <c r="I74" s="17" t="n"/>
+      <c r="J74" s="17" t="n"/>
+      <c r="K74" s="17" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
           <t>에스티팜</t>
         </is>
       </c>
-      <c r="B56" s="11" t="n">
+      <c r="B75" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="C56" s="11" t="n">
-        <v>244188000</v>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>5.31%→5.49%</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="C75" s="11" t="n">
+        <v>241927000</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>5.31%→5.65%</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
         <is>
           <t>237→256</t>
         </is>
       </c>
-      <c r="G56" s="17" t="n"/>
-      <c r="H56" s="17" t="n"/>
-      <c r="I56" s="17" t="n"/>
-      <c r="J56" s="17" t="n"/>
-      <c r="K56" s="17" t="n"/>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="G75" s="17" t="n"/>
+      <c r="H75" s="17" t="n"/>
+      <c r="I75" s="17" t="n"/>
+      <c r="J75" s="17" t="n"/>
+      <c r="K75" s="17" t="n"/>
+    </row>
+    <row r="77" ht="19" customHeight="1">
+      <c r="A77" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="19" t="n"/>
-      <c r="D58" s="19" t="n"/>
-      <c r="E58" s="19" t="n"/>
-      <c r="F58" s="19" t="n"/>
-      <c r="G58" s="19" t="n"/>
-      <c r="H58" s="19" t="n"/>
-      <c r="I58" s="19" t="n"/>
-      <c r="J58" s="19" t="n"/>
-      <c r="K58" s="19" t="n"/>
+      <c r="B77" s="19" t="n"/>
+      <c r="C77" s="19" t="n"/>
+      <c r="D77" s="19" t="n"/>
+      <c r="E77" s="19" t="n"/>
+      <c r="F77" s="19" t="n"/>
+      <c r="G77" s="19" t="n"/>
+      <c r="H77" s="19" t="n"/>
+      <c r="I77" s="19" t="n"/>
+      <c r="J77" s="19" t="n"/>
+      <c r="K77" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A58:K58"/>
+  <mergeCells count="21">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="G52:K52"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="G30:K30"/>
+    <mergeCell ref="G68:K68"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="G49:K49"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260813.xlsx
+++ b/reports/pdf_rolling5_20260813.xlsx
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-341426800</v>
+        <v>-211173820</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.21%</t>
+          <t>0.09%→0.05%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>49→36</t>
+          <t>26→13</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-211173820</v>
+        <v>-341426800</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.09%→0.05%</t>
+          <t>0.33%→0.21%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>49→36</t>
         </is>
       </c>
     </row>
@@ -2558,23 +2558,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>49749600</v>
+        <v>31737600</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.98%</t>
+          <t>2.57%→2.68%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>138→144</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2602,23 +2602,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>31737600</v>
+        <v>58869600</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.57%→2.68%</t>
+          <t>2.83%→3.04%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>138→144</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -2646,44 +2646,44 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>58869600</v>
+        <v>49749600</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.83%→3.04%</t>
+          <t>2.80%→2.98%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-40261000</v>
+        <v>-28108600</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.61%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>69→56</t>
+          <t>26→13</t>
         </is>
       </c>
     </row>
@@ -2695,23 +2695,23 @@
       <c r="E63" s="17" t="n"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-28108600</v>
+        <v>-40261000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.75%→0.61%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>69→56</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260813.xlsx
+++ b/reports/pdf_rolling5_20260813.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,732억   ·   현금 263억(5.4%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 11종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,744억   ·   현금 263억(5.4%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 11종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-211173820</v>
+        <v>-341426800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.09%→0.05%</t>
+          <t>0.33%→0.21%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>49→36</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-341426800</v>
+        <v>-211173820</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.21%</t>
+          <t>0.09%→0.05%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>49→36</t>
+          <t>26→13</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,183억   ·   현금 21억(0.5%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,037억   ·   현금 21억(0.5%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1491,7 +1491,7 @@
     <row r="29" ht="19" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,694억   ·   현금 60억(2.2%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 4종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,731억   ·   현금 60억(2.2%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 4종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B29" s="4" t="n"/>
@@ -1587,7 +1587,7 @@
         <v>70</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>4275180000</v>
+        <v>4287360000</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>-281</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1970647380</v>
+        <v>-1976261760</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>50</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>3938220000</v>
+        <v>3949440000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>-148</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-3387009600</v>
+        <v>-3396659200</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>48</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>533744640</v>
+        <v>535265280</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>-122</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-2556473400</v>
+        <v>-2563756800</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>33</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>7355205000</v>
+        <v>7376160000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>-34</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1630184400</v>
+        <v>-1634828800</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>-23</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2144188800</v>
+        <v>-2150297600</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>-20</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-982800000</v>
+        <v>-985600000</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>-5</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1432080000</v>
+        <v>-1436160000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>-3</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-34138260</v>
+        <v>-34235520</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,418억   ·   현금 49억(2.1%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 6종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,349억   ·   현금 49억(2.1%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
@@ -1964,7 +1964,7 @@
         <v>233</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>3500615300</v>
+        <v>3490258450</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>-400</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2026648000</v>
+        <v>-2020652000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>84</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>2359375200</v>
+        <v>2352394800</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>-156</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1215380400</v>
+        <v>-1211784600</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>82</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>5598632000</v>
+        <v>5582068000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>-120</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-12877800000</v>
+        <v>-12839700000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>52</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1158258400</v>
+        <v>1154831600</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>-102</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1396278000</v>
+        <v>-1392147000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>44</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1687972000</v>
+        <v>1682978000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>-20</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1159340000</v>
+        <v>-1155910000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>40</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>2364648000</v>
+        <v>2357652000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
     <row r="51" ht="19" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 291억   ·   현금 15억(5.0%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 9종목  /  매도 12종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 294억   ·   현금 15억(5.0%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 9종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>
@@ -2301,11 +2301,11 @@
         <v>224</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>429856000</v>
+        <v>432409600</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>5.37%→6.89%</t>
+          <t>5.35%→6.87%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2322,11 +2322,11 @@
         <v>-296</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-195940160</v>
+        <v>-202913920</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>7.98%→7.30%</t>
+          <t>8.18%→7.50%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2345,11 +2345,11 @@
         <v>62</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>19460560</v>
+        <v>18447480</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>0.60%→0.67%</t>
+          <t>0.57%→0.63%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2366,11 +2366,11 @@
         <v>-199</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-51043500</v>
+        <v>-51799700</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.21%</t>
+          <t>0.39%→0.21%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2389,11 +2389,11 @@
         <v>47</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>136807600</v>
+        <v>133057000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>7.16%→7.66%</t>
+          <t>6.90%→7.38%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2410,11 +2410,11 @@
         <v>-117</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-225412200</v>
+        <v>-236527200</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>3.48%→2.69%</t>
+          <t>3.62%→2.80%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2433,7 +2433,7 @@
         <v>36</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>28509120</v>
+        <v>27524160</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
@@ -2454,11 +2454,11 @@
         <v>-65</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-89364600</v>
+        <v>-88327200</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>1.69%→1.37%</t>
+          <t>1.65%→1.35%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2477,11 +2477,11 @@
         <v>34</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>46460320</v>
+        <v>47002960</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>3.10%→3.27%</t>
+          <t>3.11%→3.28%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2498,11 +2498,11 @@
         <v>-53</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-31901760</v>
+        <v>-32707360</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.79%→0.68%</t>
+          <t>0.81%→0.69%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2521,11 +2521,11 @@
         <v>22</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>28006000</v>
+        <v>26267120</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.10%</t>
+          <t>0.00%→0.09%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2542,11 +2542,11 @@
         <v>-38</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-42540240</v>
+        <v>-45341600</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>0.25%→0.10%</t>
+          <t>0.26%→0.10%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2558,23 +2558,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>31737600</v>
+        <v>49293600</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>2.57%→2.68%</t>
+          <t>2.74%→2.93%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>138→144</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2586,7 +2586,7 @@
         <v>-29</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-32354720</v>
+        <v>-32817560</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2602,23 +2602,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>58869600</v>
+        <v>32056800</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.83%→3.04%</t>
+          <t>2.57%→2.69%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>138→144</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -2630,11 +2630,11 @@
         <v>-18</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-49795200</v>
+        <v>-49863600</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>2.62%→2.44%</t>
+          <t>2.59%→2.43%</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -2646,23 +2646,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>49749600</v>
+        <v>60556800</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.98%</t>
+          <t>2.88%→3.10%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -2674,11 +2674,11 @@
         <v>-13</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-28108600</v>
+        <v>-30628000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.21%→0.11%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -2702,7 +2702,7 @@
         <v>-13</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-40261000</v>
+        <v>-40656200</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2730,11 +2730,11 @@
         <v>-5</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-76190000</v>
+        <v>-87020000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.36%→2.09%</t>
+          <t>2.66%→2.37%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2758,7 +2758,7 @@
         <v>-3</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-8755200</v>
+        <v>-8812200</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 615억   ·   현금 20억(3.3%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 6종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억   ·   현금 20억(3.3%)      오늘 2026-08-13  vs  5일전 2026-08-06      매수 6종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B67" s="4" t="n"/>
@@ -2870,7 +2870,7 @@
         <v>130</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>520565500</v>
+        <v>524940000</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>-25</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-798787500</v>
+        <v>-805500000</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>107</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>839104700</v>
+        <v>846156000</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>-21</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-793432500</v>
+        <v>-800100000</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>89</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>327261900</v>
+        <v>330012000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>-12</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-582624000</v>
+        <v>-587520000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>30</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>138516000</v>
+        <v>139680000</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>27</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>561953700</v>
+        <v>566676000</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>19</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>241927000</v>
+        <v>243960000</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260813.xlsx
+++ b/reports/pdf_rolling5_20260813.xlsx
@@ -2558,23 +2558,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>49293600</v>
+        <v>32056800</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>2.74%→2.93%</t>
+          <t>2.57%→2.69%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>138→144</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2602,23 +2602,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>32056800</v>
+        <v>60556800</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.57%→2.69%</t>
+          <t>2.88%→3.10%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>138→144</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -2646,44 +2646,44 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>60556800</v>
+        <v>49293600</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.88%→3.10%</t>
+          <t>2.74%→2.93%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-30628000</v>
+        <v>-40656200</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.11%</t>
+          <t>0.75%→0.61%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>69→56</t>
         </is>
       </c>
     </row>
@@ -2695,23 +2695,23 @@
       <c r="E63" s="17" t="n"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-40656200</v>
+        <v>-30628000</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.61%</t>
+          <t>0.21%→0.11%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>69→56</t>
+          <t>26→13</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260813.xlsx
+++ b/reports/pdf_rolling5_20260813.xlsx
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-341426800</v>
+        <v>-211173820</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.21%</t>
+          <t>0.09%→0.05%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>49→36</t>
+          <t>26→13</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-211173820</v>
+        <v>-341426800</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.09%→0.05%</t>
+          <t>0.33%→0.21%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>49→36</t>
         </is>
       </c>
     </row>
@@ -2558,23 +2558,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>32056800</v>
+        <v>49293600</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>2.57%→2.69%</t>
+          <t>2.74%→2.93%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>138→144</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2646,23 +2646,23 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>49293600</v>
+        <v>32056800</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.74%→2.93%</t>
+          <t>2.57%→2.69%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>138→144</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260813.xlsx
+++ b/reports/pdf_rolling5_20260813.xlsx
@@ -855,23 +855,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-211173820</v>
+        <v>-341426800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.09%→0.05%</t>
+          <t>0.33%→0.21%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>49→36</t>
         </is>
       </c>
     </row>
@@ -899,23 +899,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-341426800</v>
+        <v>-211173820</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.21%</t>
+          <t>0.09%→0.05%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>49→36</t>
+          <t>26→13</t>
         </is>
       </c>
     </row>
@@ -2558,23 +2558,23 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>49293600</v>
+        <v>60556800</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>2.74%→2.93%</t>
+          <t>2.88%→3.10%</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -2602,23 +2602,23 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B61" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>60556800</v>
+        <v>32056800</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>2.88%→3.10%</t>
+          <t>2.57%→2.69%</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>138→144</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -2646,44 +2646,44 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B62" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>32056800</v>
+        <v>49293600</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>2.57%→2.69%</t>
+          <t>2.74%→2.93%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>138→144</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>네패스아크</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-40656200</v>
+        <v>-30628000</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.61%</t>
+          <t>0.21%→0.11%</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>69→56</t>
+          <t>26→13</t>
         </is>
       </c>
     </row>
@@ -2695,23 +2695,23 @@
       <c r="E63" s="17" t="n"/>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>네패스아크</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-30628000</v>
+        <v>-40656200</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.11%</t>
+          <t>0.75%→0.61%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>26→13</t>
+          <t>69→56</t>
         </is>
       </c>
     </row>
